--- a/inasistencias-5a-Electornica/alumnos-5a-Electronica.xlsx
+++ b/inasistencias-5a-Electornica/alumnos-5a-Electronica.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="asistencia" sheetId="1" state="visible" r:id="rId3"/>
@@ -14,6 +14,7 @@
     <sheet name="2-RealColBase" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="3-ThevYNor" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="4-DivResistivo" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="positivos" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="105">
   <si>
     <t xml:space="preserve">nota carpeta</t>
   </si>
@@ -318,10 +319,10 @@
     <t xml:space="preserve">valoracion</t>
   </si>
   <si>
-    <t xml:space="preserve">6- oscilador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">falta lujan que lo habia pedido con anterioridad</t>
+    <t xml:space="preserve">6.1-Diseño oscilador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2-Diseño-TR</t>
   </si>
   <si>
     <t xml:space="preserve">Calificación/10,00</t>
@@ -429,7 +430,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -450,7 +451,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -471,10 +472,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -831,13 +828,13 @@
         <v>46190</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>46225</v>
+        <v>46197</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>46232</v>
+        <v>46204</v>
       </c>
       <c r="AF2" s="3" t="n">
-        <v>46239</v>
+        <v>46211</v>
       </c>
       <c r="AG2" s="3" t="n">
         <v>46246</v>
@@ -988,7 +985,16 @@
       <c r="AB3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AC3" s="5" t="s">
+      <c r="AC3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF3" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1064,8 +1070,17 @@
       <c r="AB4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AC4" s="5" t="s">
-        <v>13</v>
+      <c r="AC4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF4" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1151,6 +1166,15 @@
       <c r="AC5" s="6" t="s">
         <v>14</v>
       </c>
+      <c r="AD5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF5" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -1224,7 +1248,16 @@
       <c r="AB6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AC6" s="5" t="s">
+      <c r="AC6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF6" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1302,7 +1335,16 @@
       <c r="AB7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AC7" s="5" t="s">
+      <c r="AC7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF7" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1378,7 +1420,16 @@
       <c r="AB8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AC8" s="5" t="s">
+      <c r="AC8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF8" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1454,7 +1505,16 @@
       <c r="AB9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AC9" s="5" t="s">
+      <c r="AC9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF9" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1530,7 +1590,16 @@
       <c r="AB10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AC10" s="5" t="s">
+      <c r="AC10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF10" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1606,8 +1675,17 @@
       <c r="AB11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AC11" s="5" t="s">
-        <v>13</v>
+      <c r="AC11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF11" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1682,7 +1760,16 @@
       <c r="AB12" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AC12" s="5" t="s">
+      <c r="AC12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF12" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1758,7 +1845,16 @@
       <c r="AB13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AC13" s="5" t="s">
+      <c r="AC13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF13" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1838,7 +1934,16 @@
       <c r="AB14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AC14" s="5" t="s">
+      <c r="AC14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF14" s="2" t="s">
         <v>13</v>
       </c>
       <c r="XDS14" s="2"/>
@@ -1954,6 +2059,15 @@
         <v>13</v>
       </c>
       <c r="AC15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF15" s="2" t="s">
         <v>13</v>
       </c>
       <c r="AKW15" s="1"/>
@@ -2115,6 +2229,15 @@
       <c r="AC16" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="AD16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF16" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="XDS16" s="2"/>
       <c r="XDT16" s="2"/>
       <c r="XDU16" s="2"/>
@@ -2229,6 +2352,15 @@
       <c r="AC17" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="AD17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF17" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="XDS17" s="2"/>
       <c r="XDT17" s="2"/>
       <c r="XDU17" s="2"/>
@@ -2341,6 +2473,15 @@
         <v>13</v>
       </c>
       <c r="AC18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF18" s="2" t="s">
         <v>13</v>
       </c>
       <c r="AKW18" s="1"/>
@@ -2507,6 +2648,15 @@
       <c r="AC19" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="AD19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF19" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="AKW19" s="1"/>
       <c r="AKX19" s="1"/>
       <c r="AKY19" s="1"/>
@@ -2666,6 +2816,15 @@
       <c r="AC20" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="AD20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF20" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
@@ -2739,7 +2898,16 @@
       <c r="AB21" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AC21" s="5" t="s">
+      <c r="AC21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF21" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2815,7 +2983,16 @@
       <c r="AB22" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AC22" s="5" t="s">
+      <c r="AC22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="XDS22" s="2"/>
@@ -2930,7 +3107,16 @@
       <c r="AB23" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AC23" s="5" t="s">
+      <c r="AC23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF23" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3008,6 +3194,15 @@
         <v>13</v>
       </c>
       <c r="AC24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF24" s="2" t="s">
         <v>13</v>
       </c>
       <c r="AKW24" s="1"/>
@@ -3167,7 +3362,16 @@
       <c r="AB25" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AC25" s="5" t="s">
+      <c r="AC25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF25" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3235,6 +3439,18 @@
       <c r="AC26" s="2" t="n">
         <f aca="false">COUNTIF(AC3:AC25,"P")</f>
         <v>22</v>
+      </c>
+      <c r="AD26" s="2" t="n">
+        <f aca="false">COUNTIF(AD3:AD25,"P")</f>
+        <v>19</v>
+      </c>
+      <c r="AE26" s="2" t="n">
+        <f aca="false">COUNTIF(AE3:AE25,"P")</f>
+        <v>21</v>
+      </c>
+      <c r="AF26" s="2" t="n">
+        <f aca="false">COUNTIF(AF3:AF25,"P")</f>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -3271,9 +3487,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.07"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16345" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="9.66"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="15" min="5" style="0" width="9.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16346" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3316,22 +3532,28 @@
         <v>93</v>
       </c>
       <c r="L2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>97</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3356,26 +3578,31 @@
       <c r="G3" s="4" t="n">
         <v>8</v>
       </c>
+      <c r="H3" s="4"/>
       <c r="I3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>46213</v>
+      </c>
       <c r="K3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L3" s="1" t="n">
-        <v>10</v>
-      </c>
+      <c r="L3" s="1"/>
       <c r="M3" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="N3" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(E3,F3,G3,I3,K3,L3,M3),0)</f>
-        <v>6</v>
-      </c>
-      <c r="O3" s="4" t="str">
-        <f aca="false">IF(N3&gt;6,"TEA",IF(N3&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+      <c r="P3" s="4" t="n">
+        <f aca="false">ROUND(AVERAGE(E3,F3,G3,I3,K3,M3,O3),0)</f>
+        <v>7</v>
+      </c>
+      <c r="Q3" s="1" t="str">
+        <f aca="false">IF(P3&gt;6,"TEA",IF(P3&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3400,26 +3627,33 @@
       <c r="G4" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="H4" s="4"/>
       <c r="I4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>46176</v>
+      </c>
       <c r="K4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>46176</v>
+      </c>
+      <c r="M4" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="M4" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(E4,F4,G4,I4,K4,L4,M4),0)</f>
-        <v>6</v>
-      </c>
-      <c r="O4" s="4" t="str">
-        <f aca="false">IF(N4&gt;6,"TEA",IF(N4&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <f aca="false">ROUND(AVERAGE(E4,F4,G4,I4,K4,M4,O4),0)</f>
+        <v>8</v>
+      </c>
+      <c r="Q4" s="1" t="str">
+        <f aca="false">IF(P4&gt;6,"TEA",IF(P4&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
       </c>
     </row>
     <row r="5" s="6" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3435,28 +3669,27 @@
       <c r="G5" s="8" t="n">
         <v>1</v>
       </c>
+      <c r="H5" s="8"/>
       <c r="I5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L5" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="L5" s="1"/>
       <c r="M5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="N5" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(E5,F5,G5,I5,K5,L5,M5),0)</f>
-        <v>1</v>
-      </c>
-      <c r="O5" s="4" t="str">
-        <f aca="false">IF(N5&gt;6,"TEA",IF(N5&gt;3,"TEP","TED"))</f>
+      <c r="P5" s="4" t="n">
+        <f aca="false">ROUND(AVERAGE(E5,F5,G5,I5,K5,M5,O5),0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q5" s="1" t="str">
+        <f aca="false">IF(P5&gt;6,"TEA",IF(P5&gt;3,"TEP","TED"))</f>
         <v>TED</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3481,25 +3714,30 @@
       <c r="G6" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="H6" s="4"/>
       <c r="I6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>46214</v>
+      </c>
       <c r="K6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L6" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="L6" s="1"/>
       <c r="M6" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(E6,F6,G6,I6,K6,L6,M6),0)</f>
+        <v>1</v>
+      </c>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <f aca="false">ROUND(AVERAGE(E6,F6,G6,I6,K6,M6,O6),0)</f>
         <v>4</v>
       </c>
-      <c r="O6" s="4" t="str">
-        <f aca="false">IF(N6&gt;6,"TEA",IF(N6&gt;3,"TEP","TED"))</f>
+      <c r="Q6" s="1" t="str">
+        <f aca="false">IF(P6&gt;6,"TEA",IF(P6&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
     </row>
@@ -3525,24 +3763,25 @@
       <c r="G7" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="H7" s="4"/>
       <c r="I7" s="1" t="n">
         <v>10</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="M7" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="M7" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(E7,F7,G7,I7,K7,L7,M7),0)</f>
+      <c r="O7" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <f aca="false">ROUND(AVERAGE(E7,F7,G7,I7,K7,M7,O7),0)</f>
         <v>8</v>
       </c>
-      <c r="O7" s="4" t="str">
-        <f aca="false">IF(N7&gt;6,"TEA",IF(N7&gt;3,"TEP","TED"))</f>
+      <c r="Q7" s="1" t="str">
+        <f aca="false">IF(P7&gt;6,"TEA",IF(P7&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -3568,6 +3807,7 @@
       <c r="G8" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="H8" s="4"/>
       <c r="I8" s="1" t="n">
         <v>8</v>
       </c>
@@ -3575,21 +3815,25 @@
       <c r="K8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="L8" s="1" t="n">
+      <c r="L8" s="3" t="n">
+        <v>46129</v>
+      </c>
+      <c r="M8" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="M8" s="1" t="n">
+      <c r="N8" s="1"/>
+      <c r="O8" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="N8" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(E8,F8,G8,I8,K8,L8,M8),0)</f>
+      <c r="P8" s="4" t="n">
+        <f aca="false">ROUND(AVERAGE(E8,F8,G8,I8,K8,M8,O8),0)</f>
         <v>8</v>
       </c>
-      <c r="O8" s="4" t="str">
-        <f aca="false">IF(N8&gt;6,"TEA",IF(N8&gt;3,"TEP","TED"))</f>
+      <c r="Q8" s="1" t="str">
+        <f aca="false">IF(P8&gt;6,"TEA",IF(P8&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="Q8" s="1" t="n">
+      <c r="R8" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3610,28 +3854,37 @@
         <v>5</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>46204</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>46205</v>
+      </c>
       <c r="K9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L9" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="L9" s="1"/>
       <c r="M9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>46275</v>
+      </c>
+      <c r="O9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(E9,F9,G9,I9,K9,L9,M9),0)</f>
-        <v>3</v>
-      </c>
-      <c r="O9" s="4" t="str">
-        <f aca="false">IF(N9&gt;6,"TEA",IF(N9&gt;3,"TEP","TED"))</f>
-        <v>TED</v>
+      <c r="P9" s="4" t="n">
+        <f aca="false">ROUND(AVERAGE(E9,F9,G9,I9,K9,M9,O9),0)</f>
+        <v>6</v>
+      </c>
+      <c r="Q9" s="1" t="str">
+        <f aca="false">IF(P9&gt;6,"TEA",IF(P9&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3656,6 +3909,7 @@
       <c r="G10" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="H10" s="4"/>
       <c r="I10" s="1" t="n">
         <v>10</v>
       </c>
@@ -3663,18 +3917,20 @@
       <c r="K10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L10" s="1" t="n">
+      <c r="L10" s="1"/>
+      <c r="M10" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="M10" s="1" t="n">
+      <c r="N10" s="1"/>
+      <c r="O10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="N10" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(E10,F10,G10,I10,K10,L10,M10),0)</f>
+      <c r="P10" s="4" t="n">
+        <f aca="false">ROUND(AVERAGE(E10,F10,G10,I10,K10,M10,O10),0)</f>
         <v>8</v>
       </c>
-      <c r="O10" s="4" t="str">
-        <f aca="false">IF(N10&gt;6,"TEA",IF(N10&gt;3,"TEP","TED"))</f>
+      <c r="Q10" s="1" t="str">
+        <f aca="false">IF(P10&gt;6,"TEA",IF(P10&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -3698,7 +3954,10 @@
         <v>1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>46204</v>
       </c>
       <c r="I11" s="1" t="n">
         <v>1</v>
@@ -3707,19 +3966,21 @@
       <c r="K11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L11" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="L11" s="1"/>
       <c r="M11" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="N11" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(E11,F11,G11,I11,K11,L11,M11),0)</f>
-        <v>3</v>
-      </c>
-      <c r="O11" s="4" t="str">
-        <f aca="false">IF(N11&gt;6,"TEA",IF(N11&gt;3,"TEP","TED"))</f>
-        <v>TED</v>
+        <v>1</v>
+      </c>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="P11" s="4" t="n">
+        <f aca="false">ROUND(AVERAGE(E11,F11,G11,I11,K11,M11,O11),0)</f>
+        <v>4</v>
+      </c>
+      <c r="Q11" s="1" t="str">
+        <f aca="false">IF(P11&gt;6,"TEA",IF(P11&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3744,24 +4005,25 @@
       <c r="G12" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="H12" s="4"/>
       <c r="I12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L12" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="M12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(E12,F12,G12,I12,K12,L12,M12),0)</f>
+      <c r="P12" s="4" t="n">
+        <f aca="false">ROUND(AVERAGE(E12,F12,G12,I12,K12,M12,O12),0)</f>
         <v>3</v>
       </c>
-      <c r="O12" s="4" t="str">
-        <f aca="false">IF(N12&gt;6,"TEA",IF(N12&gt;3,"TEP","TED"))</f>
+      <c r="Q12" s="1" t="str">
+        <f aca="false">IF(P12&gt;6,"TEA",IF(P12&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
     </row>
@@ -3784,25 +4046,30 @@
       <c r="G13" s="2" t="n">
         <v>10</v>
       </c>
+      <c r="H13" s="2"/>
       <c r="I13" s="1" t="n">
         <v>10</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>46127</v>
       </c>
       <c r="M13" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="N13" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(E13,F13,G13,I13,K13,L13,M13),0)</f>
-        <v>8</v>
-      </c>
-      <c r="O13" s="4" t="str">
-        <f aca="false">IF(N13&gt;6,"TEA",IF(N13&gt;3,"TEP","TED"))</f>
+      <c r="P13" s="4" t="n">
+        <f aca="false">ROUND(AVERAGE(E13,F13,G13,I13,K13,M13,O13),0)</f>
+        <v>9</v>
+      </c>
+      <c r="Q13" s="1" t="str">
+        <f aca="false">IF(P13&gt;6,"TEA",IF(P13&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -3825,30 +4092,33 @@
       <c r="G14" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="H14" s="4"/>
       <c r="I14" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>46205</v>
+      </c>
       <c r="K14" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L14" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M14" s="1" t="n">
+      <c r="L14" s="1"/>
+      <c r="M14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="N14" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(E14,F14,G14,I14,K14,L14,M14),0)</f>
-        <v>7</v>
-      </c>
-      <c r="O14" s="4" t="str">
-        <f aca="false">IF(N14&gt;6,"TEA",IF(N14&gt;3,"TEP","TED"))</f>
+      <c r="P14" s="4" t="n">
+        <f aca="false">ROUND(AVERAGE(E14,F14,G14,I14,K14,M14,O14),0)</f>
+        <v>8</v>
+      </c>
+      <c r="Q14" s="1" t="str">
+        <f aca="false">IF(P14&gt;6,"TEA",IF(P14&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="Q14" s="1" t="s">
-        <v>98</v>
-      </c>
+      <c r="R14" s="1"/>
     </row>
     <row r="15" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
@@ -3872,27 +4142,31 @@
       <c r="G15" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="H15" s="4"/>
       <c r="I15" s="2" t="n">
         <v>6</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>46137</v>
+      </c>
+      <c r="M15" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="M15" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="N15" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(E15,F15,G15,I15,K15,L15,M15),0)</f>
+      <c r="N15" s="1"/>
+      <c r="O15" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P15" s="4" t="n">
+        <f aca="false">ROUND(AVERAGE(E15,F15,G15,I15,K15,M15,O15),0)</f>
         <v>8</v>
       </c>
-      <c r="O15" s="4" t="str">
-        <f aca="false">IF(N15&gt;6,"TEA",IF(N15&gt;3,"TEP","TED"))</f>
+      <c r="Q15" s="1" t="str">
+        <f aca="false">IF(P15&gt;6,"TEA",IF(P15&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="XDO15" s="1"/>
       <c r="XDP15" s="1"/>
       <c r="XDQ15" s="1"/>
       <c r="XDR15" s="1"/>
@@ -3957,6 +4231,7 @@
       <c r="G16" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="H16" s="2"/>
       <c r="I16" s="2" t="n">
         <v>1</v>
       </c>
@@ -3964,18 +4239,19 @@
       <c r="K16" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" s="1" t="n">
+      <c r="M16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="N16" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(E16,F16,G16,I16,K16,L16,M16),0)</f>
+      <c r="P16" s="4" t="n">
+        <f aca="false">ROUND(AVERAGE(E16,F16,G16,I16,K16,M16,O16),0)</f>
         <v>3</v>
       </c>
-      <c r="O16" s="4" t="str">
-        <f aca="false">IF(N16&gt;6,"TEA",IF(N16&gt;3,"TEP","TED"))</f>
+      <c r="Q16" s="1" t="str">
+        <f aca="false">IF(P16&gt;6,"TEA",IF(P16&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
     </row>
@@ -3999,27 +4275,36 @@
         <v>7.5</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>46204</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>46212</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="N17" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(E17,F17,G17,I17,K17,L17,M17),0)</f>
-        <v>3</v>
-      </c>
-      <c r="O17" s="4" t="str">
-        <f aca="false">IF(N17&gt;6,"TEA",IF(N17&gt;3,"TEP","TED"))</f>
-        <v>TED</v>
+      <c r="M17" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <f aca="false">ROUND(AVERAGE(E17,F17,G17,I17,K17,M17,O17),0)</f>
+        <v>6</v>
+      </c>
+      <c r="Q17" s="1" t="str">
+        <f aca="false">IF(P17&gt;6,"TEA",IF(P17&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4044,28 +4329,32 @@
       <c r="G18" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="H18" s="4"/>
       <c r="I18" s="1" t="n">
         <v>10</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>46137</v>
+      </c>
+      <c r="M18" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="M18" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="N18" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(E18,F18,G18,I18,K18,L18,M18),0)</f>
-        <v>8</v>
-      </c>
-      <c r="O18" s="4" t="str">
-        <f aca="false">IF(N18&gt;6,"TEA",IF(N18&gt;3,"TEP","TED"))</f>
+      <c r="N18" s="1"/>
+      <c r="O18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <f aca="false">ROUND(AVERAGE(E18,F18,G18,I18,K18,M18,O18),0)</f>
+        <v>9</v>
+      </c>
+      <c r="Q18" s="1" t="str">
+        <f aca="false">IF(P18&gt;6,"TEA",IF(P18&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="XDO18" s="1"/>
       <c r="XDP18" s="1"/>
       <c r="XDQ18" s="1"/>
       <c r="XDR18" s="1"/>
@@ -4130,7 +4419,7 @@
       <c r="G19" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H19" s="11" t="n">
+      <c r="H19" s="3" t="n">
         <v>46130</v>
       </c>
       <c r="I19" s="1" t="n">
@@ -4138,23 +4427,28 @@
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>46137</v>
+      </c>
+      <c r="M19" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="L19" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" s="2" t="n">
+      <c r="N19" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="O19" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="N19" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(E19,F19,G19,I19,K19,L19,M19),0)</f>
-        <v>7</v>
-      </c>
-      <c r="O19" s="4" t="str">
-        <f aca="false">IF(N19&gt;6,"TEA",IF(N19&gt;3,"TEP","TED"))</f>
+      <c r="P19" s="4" t="n">
+        <f aca="false">ROUND(AVERAGE(E19,F19,G19,I19,K19,M19,O19),0)</f>
+        <v>8</v>
+      </c>
+      <c r="Q19" s="1" t="str">
+        <f aca="false">IF(P19&gt;6,"TEA",IF(P19&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="XDO19" s="1"/>
       <c r="XDP19" s="1"/>
       <c r="XDQ19" s="1"/>
       <c r="XDR19" s="1"/>
@@ -4216,25 +4510,30 @@
       <c r="G20" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="H20" s="4"/>
       <c r="I20" s="2" t="n">
         <v>8</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M20" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>46137</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="N20" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(E20,F20,G20,I20,K20,L20,M20),0)</f>
+      <c r="P20" s="4" t="n">
+        <f aca="false">ROUND(AVERAGE(E20,F20,G20,I20,K20,M20,O20),0)</f>
         <v>8</v>
       </c>
-      <c r="O20" s="4" t="str">
-        <f aca="false">IF(N20&gt;6,"TEA",IF(N20&gt;3,"TEP","TED"))</f>
+      <c r="Q20" s="1" t="str">
+        <f aca="false">IF(P20&gt;6,"TEA",IF(P20&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -4260,25 +4559,29 @@
       <c r="G21" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="H21" s="4"/>
       <c r="I21" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>46206</v>
       </c>
       <c r="K21" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L21" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="M21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="N21" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(E21,F21,G21,I21,K21,L21,M21),0)</f>
-        <v>3</v>
-      </c>
-      <c r="O21" s="4" t="str">
-        <f aca="false">IF(N21&gt;6,"TEA",IF(N21&gt;3,"TEP","TED"))</f>
-        <v>TED</v>
+      <c r="P21" s="4" t="n">
+        <f aca="false">ROUND(AVERAGE(E21,F21,G21,I21,K21,M21,O21),0)</f>
+        <v>4</v>
+      </c>
+      <c r="Q21" s="1" t="str">
+        <f aca="false">IF(P21&gt;6,"TEA",IF(P21&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4303,24 +4606,25 @@
       <c r="G22" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="H22" s="2"/>
       <c r="I22" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K22" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L22" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="M22" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="N22" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(E22,F22,G22,I22,K22,L22,M22),0)</f>
+        <v>1</v>
+      </c>
+      <c r="O22" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="P22" s="4" t="n">
+        <f aca="false">ROUND(AVERAGE(E22,F22,G22,I22,K22,M22,O22),0)</f>
         <v>3</v>
       </c>
-      <c r="O22" s="4" t="str">
-        <f aca="false">IF(N22&gt;6,"TEA",IF(N22&gt;3,"TEP","TED"))</f>
+      <c r="Q22" s="1" t="str">
+        <f aca="false">IF(P22&gt;6,"TEA",IF(P22&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
     </row>
@@ -4346,24 +4650,28 @@
       <c r="G23" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="H23" s="4"/>
       <c r="I23" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>46127</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="L23" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="M23" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="N23" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(E23,F23,G23,I23,K23,L23,M23),0)</f>
-        <v>8</v>
-      </c>
-      <c r="O23" s="4" t="str">
-        <f aca="false">IF(N23&gt;6,"TEA",IF(N23&gt;3,"TEP","TED"))</f>
+      <c r="O23" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="P23" s="4" t="n">
+        <f aca="false">ROUND(AVERAGE(E23,F23,G23,I23,K23,M23,O23),0)</f>
+        <v>9</v>
+      </c>
+      <c r="Q23" s="1" t="str">
+        <f aca="false">IF(P23&gt;6,"TEA",IF(P23&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -4389,33 +4697,36 @@
       <c r="G24" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H24" s="11" t="n">
+      <c r="H24" s="3" t="n">
         <v>46169</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>46169</v>
+        <v>46204</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="L24" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="N24" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(E24,F24,G24,I24,K24,L24,M24),0)</f>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="O24" s="4" t="str">
-        <f aca="false">IF(N24&gt;6,"TEA",IF(N24&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
-      </c>
-      <c r="XDO24" s="1"/>
+      <c r="N24" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P24" s="4" t="n">
+        <f aca="false">ROUND(AVERAGE(E24,F24,G24,I24,K24,M24,O24),0)</f>
+        <v>7</v>
+      </c>
+      <c r="Q24" s="1" t="str">
+        <f aca="false">IF(P24&gt;6,"TEA",IF(P24&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
       <c r="XDP24" s="1"/>
       <c r="XDQ24" s="1"/>
       <c r="XDR24" s="1"/>
@@ -4480,30 +4791,37 @@
       <c r="G25" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="H25" s="4"/>
       <c r="I25" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>46214</v>
+      </c>
       <c r="K25" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L25" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="L25" s="1"/>
       <c r="M25" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="O25" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(E25,F25,G25,I25,K25,L25,M25),0)</f>
-        <v>5</v>
-      </c>
-      <c r="O25" s="4" t="str">
-        <f aca="false">IF(N25&gt;6,"TEA",IF(N25&gt;3,"TEP","TED"))</f>
+      <c r="P25" s="4" t="n">
+        <f aca="false">ROUND(AVERAGE(E25,F25,G25,I25,K25,M25,O25),0)</f>
+        <v>6</v>
+      </c>
+      <c r="Q25" s="1" t="str">
+        <f aca="false">IF(P25&gt;6,"TEA",IF(P25&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G3:G25">
+  <conditionalFormatting sqref="G3:H25">
     <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>6</formula>
     </cfRule>
@@ -4533,7 +4851,7 @@
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K3:K25">
+  <conditionalFormatting sqref="K3:L25">
     <cfRule type="cellIs" priority="10" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>6</formula>
     </cfRule>
@@ -4545,7 +4863,7 @@
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L3:L25">
+  <conditionalFormatting sqref="M3:N25">
     <cfRule type="cellIs" priority="13" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>6</formula>
     </cfRule>
@@ -4560,7 +4878,7 @@
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M3:M25">
+  <conditionalFormatting sqref="O3:O25">
     <cfRule type="cellIs" priority="17" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>6</formula>
     </cfRule>
@@ -4572,7 +4890,7 @@
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N3:N25">
+  <conditionalFormatting sqref="P3:P25">
     <cfRule type="cellIs" priority="20" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>6</formula>
     </cfRule>
@@ -4584,7 +4902,7 @@
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O3:O25">
+  <conditionalFormatting sqref="Q3:Q25">
     <cfRule type="cellIs" priority="23" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"TEA"</formula>
     </cfRule>
@@ -6464,4 +6782,292 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.07"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/inasistencias-5a-Electornica/alumnos-5a-Electronica.xlsx
+++ b/inasistencias-5a-Electornica/alumnos-5a-Electronica.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="asistencia" sheetId="1" state="visible" r:id="rId3"/>
@@ -15,6 +15,7 @@
     <sheet name="3-ThevYNor" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="4-DivResistivo" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="positivos" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Ravanelli" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="121">
   <si>
     <t xml:space="preserve">nota carpeta</t>
   </si>
@@ -341,6 +342,54 @@
   </si>
   <si>
     <t xml:space="preserve">totoal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ravanelli – Temas adeundados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electrónica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revision de teorema de Thevenin y Norton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polarizacion de transistores en forma estática con 2 fuentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polarizacion de transistores con realimentación colector base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polarizacion de transistores con divisor resistivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instrumental y sistemas eléctricos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sistemas de navegacion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">indicadores de vuelo RMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tipos de cabinas de aviones y sus generaciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instrumentos de abordo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tecnicas Diginales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Codigos, pasajes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algebra de boole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compuertas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diagramas de Karnagh</t>
   </si>
 </sst>
 </file>
@@ -430,7 +479,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -452,6 +501,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -724,8 +777,7 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="7" min="7" style="1" width="10.76"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="12" min="8" style="1" width="8.86"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="13" style="1" width="13.56"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="21" min="14" style="1" width="8.86"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="25" min="23" style="1" width="8.86"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="30" min="14" style="1" width="8.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="985" min="985" style="1" width="9.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16346" style="1" width="10.58"/>
   </cols>
@@ -997,6 +1049,12 @@
       <c r="AF3" s="5" t="s">
         <v>13</v>
       </c>
+      <c r="AG3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH3" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
@@ -1082,97 +1140,109 @@
       <c r="AF4" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
+      <c r="AG4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH4" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="7" t="s">
+      <c r="E5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" s="7" t="s">
+      <c r="J5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="M5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="N5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P5" s="7" t="s">
+      <c r="P5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="Q5" s="7" t="s">
+      <c r="Q5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="R5" s="6" t="s">
+      <c r="R5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="6" t="s">
+      <c r="T5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="V5" s="6" t="s">
+      <c r="V5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="W5" s="6" t="n">
+      <c r="W5" s="7" t="n">
         <f aca="false">COUNTIF(E5:V5,"P")</f>
         <v>2</v>
       </c>
-      <c r="X5" s="6" t="n">
+      <c r="X5" s="7" t="n">
         <f aca="false">COUNTIF(E5:V5,"A")</f>
         <v>10</v>
       </c>
-      <c r="Y5" s="6" t="n">
+      <c r="Y5" s="7" t="n">
         <f aca="false">SUM(W5:X5)</f>
         <v>12</v>
       </c>
-      <c r="Z5" s="8" t="n">
+      <c r="Z5" s="9" t="n">
         <f aca="false">ROUND(W5*10/Y5,0)</f>
         <v>2</v>
       </c>
-      <c r="AA5" s="6" t="s">
+      <c r="AA5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="AB5" s="6" t="s">
+      <c r="AB5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="AC5" s="6" t="s">
+      <c r="AC5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="AD5" s="6" t="s">
+      <c r="AD5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="AE5" s="6" t="s">
+      <c r="AE5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="AF5" s="6" t="s">
+      <c r="AF5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH5" s="7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1260,6 +1330,12 @@
       <c r="AF6" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="AG6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH6" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -1347,6 +1423,12 @@
       <c r="AF7" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="AG7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH7" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
@@ -1432,6 +1514,12 @@
       <c r="AF8" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="AG8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH8" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
@@ -1517,6 +1605,12 @@
       <c r="AF9" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="AG9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH9" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
@@ -1602,6 +1696,12 @@
       <c r="AF10" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="AG10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH10" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
@@ -1687,6 +1787,12 @@
       <c r="AF11" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="AG11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH11" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
@@ -1772,6 +1878,12 @@
       <c r="AF12" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="AG12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH12" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
@@ -1857,6 +1969,12 @@
       <c r="AF13" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="AG13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH13" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
@@ -1944,6 +2062,12 @@
         <v>13</v>
       </c>
       <c r="AF14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH14" s="6" t="s">
         <v>13</v>
       </c>
       <c r="XDS14" s="2"/>
@@ -2068,6 +2192,12 @@
         <v>13</v>
       </c>
       <c r="AF15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH15" s="2" t="s">
         <v>13</v>
       </c>
       <c r="AKW15" s="1"/>
@@ -2238,6 +2368,12 @@
       <c r="AF16" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="AG16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH16" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="XDS16" s="2"/>
       <c r="XDT16" s="2"/>
       <c r="XDU16" s="2"/>
@@ -2361,6 +2497,12 @@
       <c r="AF17" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="AG17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH17" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="XDS17" s="2"/>
       <c r="XDT17" s="2"/>
       <c r="XDU17" s="2"/>
@@ -2482,6 +2624,12 @@
         <v>13</v>
       </c>
       <c r="AF18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH18" s="2" t="s">
         <v>13</v>
       </c>
       <c r="AKW18" s="1"/>
@@ -2657,6 +2805,12 @@
       <c r="AF19" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="AG19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH19" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="AKW19" s="1"/>
       <c r="AKX19" s="1"/>
       <c r="AKY19" s="1"/>
@@ -2825,6 +2979,12 @@
       <c r="AF20" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="AG20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH20" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
@@ -2910,6 +3070,12 @@
       <c r="AF21" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="AG21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH21" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
@@ -2994,6 +3160,12 @@
       </c>
       <c r="AF22" s="2" t="s">
         <v>13</v>
+      </c>
+      <c r="AG22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH22" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="XDS22" s="2"/>
       <c r="XDT22" s="2"/>
@@ -3119,6 +3291,12 @@
       <c r="AF23" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="AG23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH23" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="24" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
@@ -3203,6 +3381,12 @@
         <v>13</v>
       </c>
       <c r="AF24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH24" s="2" t="s">
         <v>13</v>
       </c>
       <c r="AKW24" s="1"/>
@@ -3374,6 +3558,12 @@
       <c r="AF25" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="AG25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH25" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
@@ -3450,6 +3640,14 @@
       </c>
       <c r="AF26" s="2" t="n">
         <f aca="false">COUNTIF(AF3:AF25,"P")</f>
+        <v>20</v>
+      </c>
+      <c r="AG26" s="2" t="n">
+        <f aca="false">COUNTIF(AG3:AG25,"P")</f>
+        <v>17</v>
+      </c>
+      <c r="AH26" s="2" t="n">
+        <f aca="false">COUNTIF(AH3:AH25,"P")</f>
         <v>20</v>
       </c>
     </row>
@@ -3487,8 +3685,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.07"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="9.66"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="15" min="5" style="0" width="9.66"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="4" style="1" width="9.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16346" style="1" width="10.58"/>
   </cols>
   <sheetData>
@@ -3572,7 +3769,7 @@
       <c r="E3" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="F3" s="9" t="n">
+      <c r="F3" s="10" t="n">
         <v>7.5</v>
       </c>
       <c r="G3" s="4" t="n">
@@ -3588,11 +3785,9 @@
       <c r="K3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L3" s="1"/>
       <c r="M3" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="1"/>
       <c r="O3" s="1" t="n">
         <v>9</v>
       </c>
@@ -3600,7 +3795,7 @@
         <f aca="false">ROUND(AVERAGE(E3,F3,G3,I3,K3,M3,O3),0)</f>
         <v>7</v>
       </c>
-      <c r="Q3" s="1" t="str">
+      <c r="Q3" s="4" t="str">
         <f aca="false">IF(P3&gt;6,"TEA",IF(P3&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -3643,7 +3838,6 @@
       <c r="M4" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="N4" s="1"/>
       <c r="O4" s="1" t="n">
         <v>10</v>
       </c>
@@ -3651,43 +3845,43 @@
         <f aca="false">ROUND(AVERAGE(E4,F4,G4,I4,K4,M4,O4),0)</f>
         <v>8</v>
       </c>
-      <c r="Q4" s="1" t="str">
+      <c r="Q4" s="4" t="str">
         <f aca="false">IF(P4&gt;6,"TEA",IF(P4&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
-    <row r="5" s="6" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
+    <row r="5" s="7" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="8"/>
-      <c r="I5" s="6" t="n">
+      <c r="G5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="9"/>
+      <c r="I5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L5" s="1"/>
-      <c r="M5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" s="6" t="n">
+      <c r="M5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="7" t="n">
         <v>2</v>
       </c>
       <c r="P5" s="4" t="n">
         <f aca="false">ROUND(AVERAGE(E5,F5,G5,I5,K5,M5,O5),0)</f>
         <v>1</v>
       </c>
-      <c r="Q5" s="1" t="str">
+      <c r="Q5" s="4" t="str">
         <f aca="false">IF(P5&gt;6,"TEA",IF(P5&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
@@ -3724,11 +3918,9 @@
       <c r="K6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L6" s="1"/>
       <c r="M6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="1"/>
       <c r="O6" s="1" t="n">
         <v>10</v>
       </c>
@@ -3736,7 +3928,7 @@
         <f aca="false">ROUND(AVERAGE(E6,F6,G6,I6,K6,M6,O6),0)</f>
         <v>4</v>
       </c>
-      <c r="Q6" s="1" t="str">
+      <c r="Q6" s="4" t="str">
         <f aca="false">IF(P6&gt;6,"TEA",IF(P6&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
@@ -3780,7 +3972,7 @@
         <f aca="false">ROUND(AVERAGE(E7,F7,G7,I7,K7,M7,O7),0)</f>
         <v>8</v>
       </c>
-      <c r="Q7" s="1" t="str">
+      <c r="Q7" s="4" t="str">
         <f aca="false">IF(P7&gt;6,"TEA",IF(P7&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -3801,7 +3993,7 @@
       <c r="E8" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="10" t="n">
         <v>9</v>
       </c>
       <c r="G8" s="4" t="n">
@@ -3811,7 +4003,6 @@
       <c r="I8" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="J8" s="1"/>
       <c r="K8" s="1" t="n">
         <v>6</v>
       </c>
@@ -3821,7 +4012,6 @@
       <c r="M8" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="N8" s="1"/>
       <c r="O8" s="1" t="n">
         <v>9</v>
       </c>
@@ -3829,7 +4019,7 @@
         <f aca="false">ROUND(AVERAGE(E8,F8,G8,I8,K8,M8,O8),0)</f>
         <v>8</v>
       </c>
-      <c r="Q8" s="1" t="str">
+      <c r="Q8" s="4" t="str">
         <f aca="false">IF(P8&gt;6,"TEA",IF(P8&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -3868,7 +4058,6 @@
       <c r="K9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L9" s="1"/>
       <c r="M9" s="1" t="n">
         <v>7</v>
       </c>
@@ -3882,7 +4071,7 @@
         <f aca="false">ROUND(AVERAGE(E9,F9,G9,I9,K9,M9,O9),0)</f>
         <v>6</v>
       </c>
-      <c r="Q9" s="1" t="str">
+      <c r="Q9" s="4" t="str">
         <f aca="false">IF(P9&gt;6,"TEA",IF(P9&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
@@ -3913,15 +4102,12 @@
       <c r="I10" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="J10" s="1"/>
       <c r="K10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L10" s="1"/>
       <c r="M10" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="N10" s="1"/>
       <c r="O10" s="1" t="n">
         <v>9</v>
       </c>
@@ -3929,7 +4115,7 @@
         <f aca="false">ROUND(AVERAGE(E10,F10,G10,I10,K10,M10,O10),0)</f>
         <v>8</v>
       </c>
-      <c r="Q10" s="1" t="str">
+      <c r="Q10" s="4" t="str">
         <f aca="false">IF(P10&gt;6,"TEA",IF(P10&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -3950,7 +4136,7 @@
       <c r="E11" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="4" t="n">
@@ -3962,15 +4148,12 @@
       <c r="I11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="1"/>
       <c r="K11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L11" s="1"/>
       <c r="M11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="N11" s="1"/>
       <c r="O11" s="1" t="n">
         <v>10</v>
       </c>
@@ -3978,7 +4161,7 @@
         <f aca="false">ROUND(AVERAGE(E11,F11,G11,I11,K11,M11,O11),0)</f>
         <v>4</v>
       </c>
-      <c r="Q11" s="1" t="str">
+      <c r="Q11" s="4" t="str">
         <f aca="false">IF(P11&gt;6,"TEA",IF(P11&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
@@ -3999,7 +4182,7 @@
       <c r="E12" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="4" t="n">
@@ -4022,7 +4205,7 @@
         <f aca="false">ROUND(AVERAGE(E12,F12,G12,I12,K12,M12,O12),0)</f>
         <v>3</v>
       </c>
-      <c r="Q12" s="1" t="str">
+      <c r="Q12" s="4" t="str">
         <f aca="false">IF(P12&gt;6,"TEA",IF(P12&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
@@ -4050,7 +4233,6 @@
       <c r="I13" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="J13" s="1"/>
       <c r="K13" s="1" t="n">
         <v>8</v>
       </c>
@@ -4060,7 +4242,6 @@
       <c r="M13" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="N13" s="1"/>
       <c r="O13" s="1" t="n">
         <v>9</v>
       </c>
@@ -4068,7 +4249,7 @@
         <f aca="false">ROUND(AVERAGE(E13,F13,G13,I13,K13,M13,O13),0)</f>
         <v>9</v>
       </c>
-      <c r="Q13" s="1" t="str">
+      <c r="Q13" s="4" t="str">
         <f aca="false">IF(P13&gt;6,"TEA",IF(P13&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -4102,7 +4283,6 @@
       <c r="K14" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L14" s="1"/>
       <c r="M14" s="2" t="n">
         <v>10</v>
       </c>
@@ -4114,7 +4294,7 @@
         <f aca="false">ROUND(AVERAGE(E14,F14,G14,I14,K14,M14,O14),0)</f>
         <v>8</v>
       </c>
-      <c r="Q14" s="1" t="str">
+      <c r="Q14" s="4" t="str">
         <f aca="false">IF(P14&gt;6,"TEA",IF(P14&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -4136,7 +4316,7 @@
       <c r="E15" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F15" s="10" t="n">
+      <c r="F15" s="11" t="n">
         <v>7.5</v>
       </c>
       <c r="G15" s="4" t="n">
@@ -4163,7 +4343,7 @@
         <f aca="false">ROUND(AVERAGE(E15,F15,G15,I15,K15,M15,O15),0)</f>
         <v>8</v>
       </c>
-      <c r="Q15" s="1" t="str">
+      <c r="Q15" s="4" t="str">
         <f aca="false">IF(P15&gt;6,"TEA",IF(P15&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -4250,7 +4430,7 @@
         <f aca="false">ROUND(AVERAGE(E16,F16,G16,I16,K16,M16,O16),0)</f>
         <v>3</v>
       </c>
-      <c r="Q16" s="1" t="str">
+      <c r="Q16" s="4" t="str">
         <f aca="false">IF(P16&gt;6,"TEA",IF(P16&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
@@ -4271,7 +4451,7 @@
       <c r="E17" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="10" t="n">
         <v>7.5</v>
       </c>
       <c r="G17" s="2" t="n">
@@ -4302,7 +4482,7 @@
         <f aca="false">ROUND(AVERAGE(E17,F17,G17,I17,K17,M17,O17),0)</f>
         <v>6</v>
       </c>
-      <c r="Q17" s="1" t="str">
+      <c r="Q17" s="4" t="str">
         <f aca="false">IF(P17&gt;6,"TEA",IF(P17&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
@@ -4323,7 +4503,7 @@
       <c r="E18" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="F18" s="11" t="n">
         <v>7.5</v>
       </c>
       <c r="G18" s="4" t="n">
@@ -4351,7 +4531,7 @@
         <f aca="false">ROUND(AVERAGE(E18,F18,G18,I18,K18,M18,O18),0)</f>
         <v>9</v>
       </c>
-      <c r="Q18" s="1" t="str">
+      <c r="Q18" s="4" t="str">
         <f aca="false">IF(P18&gt;6,"TEA",IF(P18&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -4413,7 +4593,7 @@
       <c r="E19" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="F19" s="11" t="n">
         <v>10</v>
       </c>
       <c r="G19" s="4" t="n">
@@ -4445,7 +4625,7 @@
         <f aca="false">ROUND(AVERAGE(E19,F19,G19,I19,K19,M19,O19),0)</f>
         <v>8</v>
       </c>
-      <c r="Q19" s="1" t="str">
+      <c r="Q19" s="4" t="str">
         <f aca="false">IF(P19&gt;6,"TEA",IF(P19&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -4532,7 +4712,7 @@
         <f aca="false">ROUND(AVERAGE(E20,F20,G20,I20,K20,M20,O20),0)</f>
         <v>8</v>
       </c>
-      <c r="Q20" s="1" t="str">
+      <c r="Q20" s="4" t="str">
         <f aca="false">IF(P20&gt;6,"TEA",IF(P20&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -4579,7 +4759,7 @@
         <f aca="false">ROUND(AVERAGE(E21,F21,G21,I21,K21,M21,O21),0)</f>
         <v>4</v>
       </c>
-      <c r="Q21" s="1" t="str">
+      <c r="Q21" s="4" t="str">
         <f aca="false">IF(P21&gt;6,"TEA",IF(P21&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
@@ -4623,7 +4803,7 @@
         <f aca="false">ROUND(AVERAGE(E22,F22,G22,I22,K22,M22,O22),0)</f>
         <v>3</v>
       </c>
-      <c r="Q22" s="1" t="str">
+      <c r="Q22" s="4" t="str">
         <f aca="false">IF(P22&gt;6,"TEA",IF(P22&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
@@ -4644,7 +4824,7 @@
       <c r="E23" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="10" t="n">
         <v>7</v>
       </c>
       <c r="G23" s="4" t="n">
@@ -4670,7 +4850,7 @@
         <f aca="false">ROUND(AVERAGE(E23,F23,G23,I23,K23,M23,O23),0)</f>
         <v>9</v>
       </c>
-      <c r="Q23" s="1" t="str">
+      <c r="Q23" s="4" t="str">
         <f aca="false">IF(P23&gt;6,"TEA",IF(P23&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -4723,7 +4903,7 @@
         <f aca="false">ROUND(AVERAGE(E24,F24,G24,I24,K24,M24,O24),0)</f>
         <v>7</v>
       </c>
-      <c r="Q24" s="1" t="str">
+      <c r="Q24" s="4" t="str">
         <f aca="false">IF(P24&gt;6,"TEA",IF(P24&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -4801,7 +4981,6 @@
       <c r="K25" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L25" s="1"/>
       <c r="M25" s="1" t="n">
         <v>7</v>
       </c>
@@ -4815,7 +4994,7 @@
         <f aca="false">ROUND(AVERAGE(E25,F25,G25,I25,K25,M25,O25),0)</f>
         <v>6</v>
       </c>
-      <c r="Q25" s="1" t="str">
+      <c r="Q25" s="4" t="str">
         <f aca="false">IF(P25&gt;6,"TEA",IF(P25&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
@@ -5005,17 +5184,17 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
+    <row r="5" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="6" t="n">
+      <c r="E5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
@@ -5617,10 +5796,10 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="n">
+      <c r="A4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="1" t="n">
@@ -6058,10 +6237,10 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="n">
+      <c r="A4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="1" t="n">
@@ -6385,10 +6564,10 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="n">
+      <c r="A4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="1" t="n">
@@ -6831,13 +7010,13 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="n">
+      <c r="A4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -7059,6 +7238,108 @@
       </c>
       <c r="C24" s="1" t="s">
         <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52.07"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/inasistencias-5a-Electornica/alumnos-5a-Electronica.xlsx
+++ b/inasistencias-5a-Electornica/alumnos-5a-Electronica.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="asistencia" sheetId="1" state="visible" r:id="rId3"/>
@@ -16,6 +16,7 @@
     <sheet name="4-DivResistivo" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="positivos" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Ravanelli" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Evaluacion" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="122">
   <si>
     <t xml:space="preserve">nota carpeta</t>
   </si>
@@ -89,241 +90,244 @@
     <t xml:space="preserve">Damian Agustin</t>
   </si>
   <si>
+    <t xml:space="preserve">Coronel (Recur)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50094499@faa.mil.ar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recursante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recuersante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santiago Gael</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIAZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50157134@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Candelaria Luisana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FARIAS RUIZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49960662@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enfermedad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriana Berenice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCOLINO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50096602@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan Diego</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIRALDO GONZALEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95622238@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demian Ignacio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUNCAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50142917@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremias Luciano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LESME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jeremiaslesme9@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laionel Dylan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOAIZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50395668@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thiago Valentin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49602531@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thiago Gabriel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUJAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49927919@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">se retiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tahiel Eliseo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANRIQUE DI FLORIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50276004@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabrizio Juan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARTINEZ RUIZ DIAZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">martnezfabrizio84@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Franco Ezequiel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MELIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50353508@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uma Bianca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLIVERA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49679317@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delfina Elizabeth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORTEGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49988641@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alejo Julián</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PALERMO TEJADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">palermoalejo@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mateo Leonel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49880530@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ivan Manuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAVANELLI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49521904@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agustin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ajolote47356@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matias Lionel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAIGUA FRANCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49547928@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giuliana Abril</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIDELA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49676632@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">presentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">carpeta nota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-dos fuentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-real col</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-Thevenin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-Div-Reis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asistencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valoracion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1-Diseño oscilador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2-Diseño-TR</t>
+  </si>
+  <si>
     <t xml:space="preserve">Coronel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50094499@faa.mil.ar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recursante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">recuersante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santiago Gael</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIAZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50157134@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Candelaria Luisana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FARIAS RUIZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49960662@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enfermedad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriana Berenice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRANCOLINO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50096602@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juan Diego</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GIRALDO GONZALEZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95622238@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demian Ignacio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUNCAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50142917@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremias Luciano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LESME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jeremiaslesme9@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laionel Dylan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOAIZA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50395668@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thiago Valentin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUCERO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49602531@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thiago Gabriel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUJAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49927919@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">se retiro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tahiel Eliseo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANRIQUE DI FLORIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50276004@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabrizio Juan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARTINEZ RUIZ DIAZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">martnezfabrizio84@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Franco Ezequiel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MELIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50353508@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uma Bianca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLIVERA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49679317@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delfina Elizabeth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ORTEGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49988641@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alejo Julián</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PALERMO TEJADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">palermoalejo@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mateo Leonel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49880530@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ivan Manuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAVANELLI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49521904@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agustin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Romero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ajolote47356@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matias Lionel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAIGUA FRANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49547928@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Giuliana Abril</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIDELA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49676632@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">presentes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grupo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">carpeta nota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evaluacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1-dos fuentes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-real col</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-Thevenin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4-Div-Reis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asistencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valoracion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1-Diseño oscilador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2-Diseño-TR</t>
   </si>
   <si>
     <t xml:space="preserve">Calificación/10,00</t>
@@ -401,7 +405,7 @@
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -423,6 +427,14 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -479,7 +491,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -521,6 +533,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -778,8 +794,8 @@
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="12" min="8" style="1" width="8.86"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="13" style="1" width="13.56"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="30" min="14" style="1" width="8.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="985" min="985" style="1" width="9.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16346" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="984" min="984" style="1" width="9.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16345" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -895,62 +911,60 @@
         <v>46253</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>46260</v>
+        <v>46267</v>
       </c>
       <c r="AJ2" s="3" t="n">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="AN2" s="3" t="n">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>46302</v>
+        <v>46309</v>
       </c>
       <c r="AP2" s="3" t="n">
-        <v>46309</v>
+        <v>46316</v>
       </c>
       <c r="AQ2" s="3" t="n">
-        <v>46316</v>
+        <v>46323</v>
       </c>
       <c r="AR2" s="3" t="n">
-        <v>46323</v>
+        <v>46330</v>
       </c>
       <c r="AS2" s="3" t="n">
-        <v>46330</v>
+        <v>46337</v>
       </c>
       <c r="AT2" s="3" t="n">
-        <v>46337</v>
+        <v>46344</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>46344</v>
+        <v>46351</v>
       </c>
       <c r="AV2" s="3" t="n">
-        <v>46351</v>
+        <v>46358</v>
       </c>
       <c r="AW2" s="3" t="n">
-        <v>46358</v>
+        <v>46365</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>46365</v>
+        <v>46372</v>
       </c>
       <c r="AY2" s="3" t="n">
-        <v>46372</v>
+        <v>46379</v>
       </c>
       <c r="AZ2" s="3" t="n">
-        <v>46379</v>
-      </c>
-      <c r="BA2" s="3" t="n">
         <v>46386</v>
       </c>
+      <c r="BA2" s="3"/>
       <c r="BB2" s="3"/>
       <c r="BC2" s="3"/>
       <c r="BD2" s="3"/>
@@ -960,7 +974,6 @@
       <c r="BH2" s="3"/>
       <c r="BI2" s="3"/>
       <c r="BJ2" s="3"/>
-      <c r="BK2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
@@ -1052,7 +1065,22 @@
       <c r="AG3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AH3" s="6" t="s">
+      <c r="AH3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM3" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1143,8 +1171,23 @@
       <c r="AG4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AH4" s="6" t="s">
-        <v>13</v>
+      <c r="AH4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM4" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1245,6 +1288,22 @@
       <c r="AH5" s="7" t="s">
         <v>14</v>
       </c>
+      <c r="AI5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="XDR5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -1333,7 +1392,22 @@
       <c r="AG6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AH6" s="6" t="s">
+      <c r="AH6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM6" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1426,7 +1500,22 @@
       <c r="AG7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AH7" s="6" t="s">
+      <c r="AH7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM7" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1517,7 +1606,22 @@
       <c r="AG8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AH8" s="6" t="s">
+      <c r="AH8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM8" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1608,8 +1712,23 @@
       <c r="AG9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AH9" s="6" t="s">
+      <c r="AH9" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="AI9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM9" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1699,7 +1818,22 @@
       <c r="AG10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AH10" s="6" t="s">
+      <c r="AH10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM10" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1790,7 +1924,22 @@
       <c r="AG11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AH11" s="6" t="s">
+      <c r="AH11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM11" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1881,7 +2030,22 @@
       <c r="AG12" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AH12" s="6" t="s">
+      <c r="AH12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM12" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1972,7 +2136,22 @@
       <c r="AG13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AH13" s="6" t="s">
+      <c r="AH13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM13" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2067,8 +2246,23 @@
       <c r="AG14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AH14" s="6" t="s">
-        <v>13</v>
+      <c r="AH14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM14" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="XDS14" s="2"/>
       <c r="XDT14" s="2"/>
@@ -2200,6 +2394,22 @@
       <c r="AH15" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="AI15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AKV15" s="1"/>
       <c r="AKW15" s="1"/>
       <c r="AKX15" s="1"/>
       <c r="AKY15" s="1"/>
@@ -2244,7 +2454,7 @@
       <c r="AML15" s="1"/>
       <c r="AMM15" s="1"/>
       <c r="AMN15" s="1"/>
-      <c r="AMO15" s="1"/>
+      <c r="XDQ15" s="1"/>
       <c r="XDR15" s="1"/>
       <c r="XDS15" s="1"/>
       <c r="XDT15" s="1"/>
@@ -2374,6 +2584,21 @@
       <c r="AH16" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="AI16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM16" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="XDS16" s="2"/>
       <c r="XDT16" s="2"/>
       <c r="XDU16" s="2"/>
@@ -2503,6 +2728,21 @@
       <c r="AH17" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="AI17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM17" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="XDS17" s="2"/>
       <c r="XDT17" s="2"/>
       <c r="XDU17" s="2"/>
@@ -2632,6 +2872,22 @@
       <c r="AH18" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="AI18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AKV18" s="1"/>
       <c r="AKW18" s="1"/>
       <c r="AKX18" s="1"/>
       <c r="AKY18" s="1"/>
@@ -2676,7 +2932,7 @@
       <c r="AML18" s="1"/>
       <c r="AMM18" s="1"/>
       <c r="AMN18" s="1"/>
-      <c r="AMO18" s="1"/>
+      <c r="XDQ18" s="1"/>
       <c r="XDR18" s="1"/>
       <c r="XDS18" s="1"/>
       <c r="XDT18" s="1"/>
@@ -2811,6 +3067,22 @@
       <c r="AH19" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="AI19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AKV19" s="1"/>
       <c r="AKW19" s="1"/>
       <c r="AKX19" s="1"/>
       <c r="AKY19" s="1"/>
@@ -2855,7 +3127,7 @@
       <c r="AML19" s="1"/>
       <c r="AMM19" s="1"/>
       <c r="AMN19" s="1"/>
-      <c r="AMO19" s="1"/>
+      <c r="XDQ19" s="1"/>
       <c r="XDR19" s="1"/>
       <c r="XDS19" s="1"/>
       <c r="XDT19" s="1"/>
@@ -2985,6 +3257,21 @@
       <c r="AH20" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="AI20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM20" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
@@ -3073,7 +3360,22 @@
       <c r="AG21" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AH21" s="6" t="s">
+      <c r="AH21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM21" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3164,7 +3466,22 @@
       <c r="AG22" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AH22" s="6" t="s">
+      <c r="AH22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM22" s="6" t="s">
         <v>14</v>
       </c>
       <c r="XDS22" s="2"/>
@@ -3294,7 +3611,22 @@
       <c r="AG23" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AH23" s="6" t="s">
+      <c r="AH23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM23" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3389,6 +3721,22 @@
       <c r="AH24" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="AI24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AKV24" s="1"/>
       <c r="AKW24" s="1"/>
       <c r="AKX24" s="1"/>
       <c r="AKY24" s="1"/>
@@ -3433,7 +3781,7 @@
       <c r="AML24" s="1"/>
       <c r="AMM24" s="1"/>
       <c r="AMN24" s="1"/>
-      <c r="AMO24" s="1"/>
+      <c r="XDQ24" s="1"/>
       <c r="XDR24" s="1"/>
       <c r="XDS24" s="1"/>
       <c r="XDT24" s="1"/>
@@ -3561,7 +3909,22 @@
       <c r="AG25" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AH25" s="6" t="s">
+      <c r="AH25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM25" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3649,6 +4012,26 @@
       <c r="AH26" s="2" t="n">
         <f aca="false">COUNTIF(AH3:AH25,"P")</f>
         <v>20</v>
+      </c>
+      <c r="AI26" s="2" t="n">
+        <f aca="false">COUNTIF(AI3:AI25,"P")</f>
+        <v>19</v>
+      </c>
+      <c r="AJ26" s="2" t="n">
+        <f aca="false">COUNTIF(AJ3:AJ25,"P")</f>
+        <v>21</v>
+      </c>
+      <c r="AK26" s="2" t="n">
+        <f aca="false">COUNTIF(AK3:AK25,"P")</f>
+        <v>18</v>
+      </c>
+      <c r="AL26" s="2" t="n">
+        <f aca="false">COUNTIF(AL3:AL25,"P")</f>
+        <v>18</v>
+      </c>
+      <c r="AM26" s="2" t="n">
+        <f aca="false">COUNTIF(AM3:AM25,"P")</f>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -3685,7 +4068,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.07"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="4" style="1" width="9.66"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="17" min="4" style="1" width="9.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="18.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="13.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16346" style="1" width="10.58"/>
   </cols>
   <sheetData>
@@ -3752,6 +4137,9 @@
       <c r="S2" s="2" t="s">
         <v>98</v>
       </c>
+      <c r="T2" s="2" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
@@ -3799,6 +4187,9 @@
         <f aca="false">IF(P3&gt;6,"TEA",IF(P3&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="T3" s="10" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
@@ -3849,6 +4240,9 @@
         <f aca="false">IF(P4&gt;6,"TEA",IF(P4&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="T4" s="10" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="5" s="7" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="n">
@@ -3858,7 +4252,7 @@
         <v>19</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="G5" s="9" t="n">
         <v>1</v>
@@ -3885,6 +4279,9 @@
         <f aca="false">IF(P5&gt;6,"TEA",IF(P5&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
+      <c r="T5" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -3932,6 +4329,9 @@
         <f aca="false">IF(P6&gt;6,"TEA",IF(P6&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
+      <c r="T6" s="10" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="7" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -3976,6 +4376,9 @@
         <f aca="false">IF(P7&gt;6,"TEA",IF(P7&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="T7" s="10" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
@@ -4026,6 +4429,9 @@
       <c r="R8" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="T8" s="10" t="n">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
@@ -4075,6 +4481,9 @@
         <f aca="false">IF(P9&gt;6,"TEA",IF(P9&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
+      <c r="T9" s="10" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
@@ -4119,6 +4528,9 @@
         <f aca="false">IF(P10&gt;6,"TEA",IF(P10&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="T10" s="10" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
@@ -4127,7 +4539,7 @@
       <c r="B11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="11" t="s">
         <v>41</v>
       </c>
       <c r="D11" s="1" t="n">
@@ -4165,6 +4577,9 @@
         <f aca="false">IF(P11&gt;6,"TEA",IF(P11&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
+      <c r="T11" s="1" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="12" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
@@ -4209,6 +4624,9 @@
         <f aca="false">IF(P12&gt;6,"TEA",IF(P12&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
+      <c r="T12" s="1" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
@@ -4253,6 +4671,9 @@
         <f aca="false">IF(P13&gt;6,"TEA",IF(P13&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="T13" s="10" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
@@ -4298,7 +4719,9 @@
         <f aca="false">IF(P14&gt;6,"TEA",IF(P14&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="R14" s="1"/>
+      <c r="T14" s="10" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="15" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
@@ -4316,7 +4739,7 @@
       <c r="E15" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="12" t="n">
         <v>7.5</v>
       </c>
       <c r="G15" s="4" t="n">
@@ -4346,6 +4769,9 @@
       <c r="Q15" s="4" t="str">
         <f aca="false">IF(P15&gt;6,"TEA",IF(P15&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="T15" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="XDP15" s="1"/>
       <c r="XDQ15" s="1"/>
@@ -4434,6 +4860,9 @@
         <f aca="false">IF(P16&gt;6,"TEA",IF(P16&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
+      <c r="T16" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
@@ -4486,6 +4915,9 @@
         <f aca="false">IF(P17&gt;6,"TEA",IF(P17&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
+      <c r="T17" s="10" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="18" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
@@ -4503,7 +4935,7 @@
       <c r="E18" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" s="12" t="n">
         <v>7.5</v>
       </c>
       <c r="G18" s="4" t="n">
@@ -4534,6 +4966,9 @@
       <c r="Q18" s="4" t="str">
         <f aca="false">IF(P18&gt;6,"TEA",IF(P18&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="T18" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="XDP18" s="1"/>
       <c r="XDQ18" s="1"/>
@@ -4593,7 +5028,7 @@
       <c r="E19" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="12" t="n">
         <v>10</v>
       </c>
       <c r="G19" s="4" t="n">
@@ -4628,6 +5063,9 @@
       <c r="Q19" s="4" t="str">
         <f aca="false">IF(P19&gt;6,"TEA",IF(P19&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="T19" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="XDP19" s="1"/>
       <c r="XDQ19" s="1"/>
@@ -4716,6 +5154,9 @@
         <f aca="false">IF(P20&gt;6,"TEA",IF(P20&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="T20" s="10" t="n">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="21" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
@@ -4763,6 +5204,9 @@
         <f aca="false">IF(P21&gt;6,"TEA",IF(P21&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
+      <c r="T21" s="10" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="22" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
@@ -4807,6 +5251,9 @@
         <f aca="false">IF(P22&gt;6,"TEA",IF(P22&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
+      <c r="T22" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
@@ -4854,6 +5301,9 @@
         <f aca="false">IF(P23&gt;6,"TEA",IF(P23&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="T23" s="10" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="24" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
@@ -4906,6 +5356,9 @@
       <c r="Q24" s="4" t="str">
         <f aca="false">IF(P24&gt;6,"TEA",IF(P24&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="T24" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="XDP24" s="1"/>
       <c r="XDQ24" s="1"/>
@@ -4997,6 +5450,9 @@
       <c r="Q25" s="4" t="str">
         <f aca="false">IF(P25&gt;6,"TEA",IF(P25&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
+      </c>
+      <c r="T25" s="10" t="n">
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>
@@ -5121,19 +5577,19 @@
         <v>2</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5189,7 +5645,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>1</v>
@@ -5698,7 +6154,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G28" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H28" s="2" t="n">
         <f aca="false">COUNTIF(H3:H27,"&gt;0")</f>
@@ -5752,16 +6208,16 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5800,7 +6256,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>1</v>
@@ -6208,7 +6664,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6241,7 +6697,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>1</v>
@@ -6517,16 +6973,16 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6568,7 +7024,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>1</v>
@@ -7017,7 +7473,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7264,82 +7720,494 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>
